--- a/crates/xlstream-eval/tests/fixtures/text/text_value.xlsx
+++ b/crates/xlstream-eval/tests/fixtures/text/text_value.xlsx
@@ -20,48 +20,27 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
-    <t xml:space="preserve">amt</t>
+    <t xml:space="preserve">num</t>
   </si>
   <si>
-    <t xml:space="preserve">text</t>
+    <t xml:space="preserve">text_fmt</t>
   </si>
   <si>
-    <t xml:space="preserve">value</t>
+    <t xml:space="preserve">value_str</t>
   </si>
   <si>
-    <t xml:space="preserve">exact</t>
+    <t xml:space="preserve">exact_same</t>
   </si>
   <si>
-    <t xml:space="preserve">hello</t>
+    <t xml:space="preserve">exact_diff</t>
   </si>
   <si>
-    <t xml:space="preserve">WORLD</t>
+    <t xml:space="preserve">text_pct</t>
   </si>
   <si>
-    <t xml:space="preserve">  spaces  here  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">abc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">short</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ProPer Case</t>
-  </si>
-  <si>
-    <t xml:space="preserve">num123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">foo bar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">x</t>
+    <t xml:space="preserve">text_int</t>
   </si>
 </sst>
 </file>
@@ -338,7 +317,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -349,213 +328,309 @@
         <v>1</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="F1" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="0" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B2" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="0" t="str">
+        <v>1234.56</v>
+      </c>
+      <c r="B2" s="0" t="str">
         <f aca="false">TEXT(A2,"0.00")</f>
-        <v>1000.00</v>
-      </c>
-      <c r="D2" s="0" t="n">
-        <f aca="false">VALUE("123.45")</f>
-        <v>123.45</v>
+        <v>1234.56</v>
+      </c>
+      <c r="C2" s="0" t="n">
+        <f aca="false">VALUE("123.45")</f>
+        <v>123.45</v>
+      </c>
+      <c r="D2" s="1" t="b">
+        <f aca="false">EXACT("hello","hello")</f>
+        <v>1</v>
       </c>
       <c r="E2" s="1" t="b">
-        <f aca="false">EXACT(B2,"hello")</f>
-        <v>1</v>
+        <f aca="false">EXACT("hello","Hello")</f>
+        <v>0</v>
+      </c>
+      <c r="F2" s="0" t="str">
+        <f aca="false">TEXT(A2,"0%")</f>
+        <v>123456%</v>
+      </c>
+      <c r="G2" s="0" t="str">
+        <f aca="false">TEXT(A2,"#,##0")</f>
+        <v>1,235</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="n">
-        <v>2500</v>
-      </c>
-      <c r="B3" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="0" t="str">
+        <v>0</v>
+      </c>
+      <c r="B3" s="0" t="str">
         <f aca="false">TEXT(A3,"0.00")</f>
-        <v>2500.00</v>
-      </c>
-      <c r="D3" s="0" t="n">
-        <f aca="false">VALUE("123.45")</f>
-        <v>123.45</v>
+        <v>0.00</v>
+      </c>
+      <c r="C3" s="0" t="n">
+        <f aca="false">VALUE("123.45")</f>
+        <v>123.45</v>
+      </c>
+      <c r="D3" s="1" t="b">
+        <f aca="false">EXACT("hello","hello")</f>
+        <v>1</v>
       </c>
       <c r="E3" s="1" t="b">
-        <f aca="false">EXACT(B3,"hello")</f>
+        <f aca="false">EXACT("hello","Hello")</f>
+        <v>0</v>
+      </c>
+      <c r="F3" s="0" t="str">
+        <f aca="false">TEXT(A3,"0%")</f>
+        <v>0%</v>
+      </c>
+      <c r="G3" s="0" t="str">
+        <f aca="false">TEXT(A3,"#,##0")</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="0" t="str">
+        <v>-99.9</v>
+      </c>
+      <c r="B4" s="0" t="str">
         <f aca="false">TEXT(A4,"0.00")</f>
-        <v>0.00</v>
-      </c>
-      <c r="D4" s="0" t="n">
-        <f aca="false">VALUE("123.45")</f>
-        <v>123.45</v>
+        <v>-99.90</v>
+      </c>
+      <c r="C4" s="0" t="n">
+        <f aca="false">VALUE("123.45")</f>
+        <v>123.45</v>
+      </c>
+      <c r="D4" s="1" t="b">
+        <f aca="false">EXACT("hello","hello")</f>
+        <v>1</v>
       </c>
       <c r="E4" s="1" t="b">
-        <f aca="false">EXACT(B4,"hello")</f>
-        <v>0</v>
+        <f aca="false">EXACT("hello","Hello")</f>
+        <v>0</v>
+      </c>
+      <c r="F4" s="0" t="str">
+        <f aca="false">TEXT(A4,"0%")</f>
+        <v>-9990%</v>
+      </c>
+      <c r="G4" s="0" t="str">
+        <f aca="false">TEXT(A4,"#,##0")</f>
+        <v>-100</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="n">
-        <v>5000</v>
-      </c>
-      <c r="B5" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="0" t="str">
+        <v>100</v>
+      </c>
+      <c r="B5" s="0" t="str">
         <f aca="false">TEXT(A5,"0.00")</f>
-        <v>5000.00</v>
-      </c>
-      <c r="D5" s="0" t="n">
-        <f aca="false">VALUE("123.45")</f>
-        <v>123.45</v>
+        <v>100.00</v>
+      </c>
+      <c r="C5" s="0" t="n">
+        <f aca="false">VALUE("123.45")</f>
+        <v>123.45</v>
+      </c>
+      <c r="D5" s="1" t="b">
+        <f aca="false">EXACT("hello","hello")</f>
+        <v>1</v>
       </c>
       <c r="E5" s="1" t="b">
-        <f aca="false">EXACT(B5,"hello")</f>
-        <v>0</v>
+        <f aca="false">EXACT("hello","Hello")</f>
+        <v>0</v>
+      </c>
+      <c r="F5" s="0" t="str">
+        <f aca="false">TEXT(A5,"0%")</f>
+        <v>10000%</v>
+      </c>
+      <c r="G5" s="0" t="str">
+        <f aca="false">TEXT(A5,"#,##0")</f>
+        <v>100</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="n">
-        <v>150</v>
-      </c>
-      <c r="B6" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="0" t="str">
+        <v>3.14159</v>
+      </c>
+      <c r="B6" s="0" t="str">
         <f aca="false">TEXT(A6,"0.00")</f>
-        <v>150.00</v>
-      </c>
-      <c r="D6" s="0" t="n">
-        <f aca="false">VALUE("123.45")</f>
-        <v>123.45</v>
+        <v>3.14</v>
+      </c>
+      <c r="C6" s="0" t="n">
+        <f aca="false">VALUE("123.45")</f>
+        <v>123.45</v>
+      </c>
+      <c r="D6" s="1" t="b">
+        <f aca="false">EXACT("hello","hello")</f>
+        <v>1</v>
       </c>
       <c r="E6" s="1" t="b">
-        <f aca="false">EXACT(B6,"hello")</f>
-        <v>0</v>
+        <f aca="false">EXACT("hello","Hello")</f>
+        <v>0</v>
+      </c>
+      <c r="F6" s="0" t="str">
+        <f aca="false">TEXT(A6,"0%")</f>
+        <v>314%</v>
+      </c>
+      <c r="G6" s="0" t="str">
+        <f aca="false">TEXT(A6,"#,##0")</f>
+        <v>3</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="n">
-        <v>3000</v>
-      </c>
-      <c r="B7" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="0" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="B7" s="0" t="str">
         <f aca="false">TEXT(A7,"0.00")</f>
-        <v>3000.00</v>
-      </c>
-      <c r="D7" s="0" t="n">
-        <f aca="false">VALUE("123.45")</f>
-        <v>123.45</v>
+        <v>0.50</v>
+      </c>
+      <c r="C7" s="0" t="n">
+        <f aca="false">VALUE("123.45")</f>
+        <v>123.45</v>
+      </c>
+      <c r="D7" s="1" t="b">
+        <f aca="false">EXACT("hello","hello")</f>
+        <v>1</v>
       </c>
       <c r="E7" s="1" t="b">
-        <f aca="false">EXACT(B7,"hello")</f>
-        <v>0</v>
+        <f aca="false">EXACT("hello","Hello")</f>
+        <v>0</v>
+      </c>
+      <c r="F7" s="0" t="str">
+        <f aca="false">TEXT(A7,"0%")</f>
+        <v>50%</v>
+      </c>
+      <c r="G7" s="0" t="str">
+        <f aca="false">TEXT(A7,"#,##0")</f>
+        <v>1</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="n">
-        <v>7500</v>
-      </c>
-      <c r="B8" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="0" t="str">
+        <v>999999</v>
+      </c>
+      <c r="B8" s="0" t="str">
         <f aca="false">TEXT(A8,"0.00")</f>
-        <v>7500.00</v>
-      </c>
-      <c r="D8" s="0" t="n">
-        <f aca="false">VALUE("123.45")</f>
-        <v>123.45</v>
+        <v>999999.00</v>
+      </c>
+      <c r="C8" s="0" t="n">
+        <f aca="false">VALUE("123.45")</f>
+        <v>123.45</v>
+      </c>
+      <c r="D8" s="1" t="b">
+        <f aca="false">EXACT("hello","hello")</f>
+        <v>1</v>
       </c>
       <c r="E8" s="1" t="b">
-        <f aca="false">EXACT(B8,"hello")</f>
-        <v>0</v>
+        <f aca="false">EXACT("hello","Hello")</f>
+        <v>0</v>
+      </c>
+      <c r="F8" s="0" t="str">
+        <f aca="false">TEXT(A8,"0%")</f>
+        <v>99999900%</v>
+      </c>
+      <c r="G8" s="0" t="str">
+        <f aca="false">TEXT(A8,"#,##0")</f>
+        <v>999,999</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="0" t="str">
+        <v>42</v>
+      </c>
+      <c r="B9" s="0" t="str">
         <f aca="false">TEXT(A9,"0.00")</f>
-        <v>250.00</v>
-      </c>
-      <c r="D9" s="0" t="n">
-        <f aca="false">VALUE("123.45")</f>
-        <v>123.45</v>
+        <v>42.00</v>
+      </c>
+      <c r="C9" s="0" t="n">
+        <f aca="false">VALUE("123.45")</f>
+        <v>123.45</v>
+      </c>
+      <c r="D9" s="1" t="b">
+        <f aca="false">EXACT("hello","hello")</f>
+        <v>1</v>
       </c>
       <c r="E9" s="1" t="b">
-        <f aca="false">EXACT(B9,"hello")</f>
-        <v>0</v>
+        <f aca="false">EXACT("hello","Hello")</f>
+        <v>0</v>
+      </c>
+      <c r="F9" s="0" t="str">
+        <f aca="false">TEXT(A9,"0%")</f>
+        <v>4200%</v>
+      </c>
+      <c r="G9" s="0" t="str">
+        <f aca="false">TEXT(A9,"#,##0")</f>
+        <v>42</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="n">
-        <v>4000</v>
-      </c>
-      <c r="B10" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" s="0" t="str">
+        <v>0.001</v>
+      </c>
+      <c r="B10" s="0" t="str">
         <f aca="false">TEXT(A10,"0.00")</f>
-        <v>4000.00</v>
-      </c>
-      <c r="D10" s="0" t="n">
-        <f aca="false">VALUE("123.45")</f>
-        <v>123.45</v>
+        <v>0.00</v>
+      </c>
+      <c r="C10" s="0" t="n">
+        <f aca="false">VALUE("123.45")</f>
+        <v>123.45</v>
+      </c>
+      <c r="D10" s="1" t="b">
+        <f aca="false">EXACT("hello","hello")</f>
+        <v>1</v>
       </c>
       <c r="E10" s="1" t="b">
-        <f aca="false">EXACT(B10,"hello")</f>
+        <f aca="false">EXACT("hello","Hello")</f>
+        <v>0</v>
+      </c>
+      <c r="F10" s="0" t="str">
+        <f aca="false">TEXT(A10,"0%")</f>
+        <v>0%</v>
+      </c>
+      <c r="G10" s="0" t="str">
+        <f aca="false">TEXT(A10,"#,##0")</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="n">
-        <v>1200</v>
-      </c>
-      <c r="B11" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="C11" s="0" t="str">
+        <v>-1</v>
+      </c>
+      <c r="B11" s="0" t="str">
         <f aca="false">TEXT(A11,"0.00")</f>
-        <v>1200.00</v>
-      </c>
-      <c r="D11" s="0" t="n">
-        <f aca="false">VALUE("123.45")</f>
-        <v>123.45</v>
+        <v>-1.00</v>
+      </c>
+      <c r="C11" s="0" t="n">
+        <f aca="false">VALUE("123.45")</f>
+        <v>123.45</v>
+      </c>
+      <c r="D11" s="1" t="b">
+        <f aca="false">EXACT("hello","hello")</f>
+        <v>1</v>
       </c>
       <c r="E11" s="1" t="b">
-        <f aca="false">EXACT(B11,"hello")</f>
-        <v>0</v>
+        <f aca="false">EXACT("hello","Hello")</f>
+        <v>0</v>
+      </c>
+      <c r="F11" s="0" t="str">
+        <f aca="false">TEXT(A11,"0%")</f>
+        <v>-100%</v>
+      </c>
+      <c r="G11" s="0" t="str">
+        <f aca="false">TEXT(A11,"#,##0")</f>
+        <v>-1</v>
       </c>
     </row>
   </sheetData>
